--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
@@ -1764,89 +1764,89 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DTD_303(70)</t>
+          <t>DTD_401(76)</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DTD_401(76)</t>
+          <t>DTD_602(70)</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DTD_402(76)</t>
+          <t>DTD_603(70)</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca3, T4-Ca4, T6-Ca3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DTD_503(70)</t>
+          <t>DTD_701(126)</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca4, T4-Ca3, T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DTD_601(126)</t>
+          <t>DTD_702(70)</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca3, T4-Ca3, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DTD_603(70)</t>
+          <t>DTD_703(70)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1854,29 +1854,29 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca1, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DTD_701(126)</t>
+          <t>EAUT_104(72)</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T4-Ca3, T6-Ca3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DTD_702(70)</t>
+          <t>EAUT_105(70)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1884,14 +1884,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca3, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DTD_703(70)</t>
+          <t>EAUT_106(70)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1899,74 +1899,74 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T4-Ca3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EAUT_104(72)</t>
+          <t>EAUT_107(70)</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca3, T4-Ca5, T6-Ca1</t>
+          <t>T4-Ca3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EAUT_105(70)</t>
+          <t>EAUT_204(80)</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca4, T4-Ca5, T6-Ca1</t>
+          <t>T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EAUT_106(70)</t>
+          <t>EAUT_205(78)</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>T4-Ca3, T4-Ca5</t>
+          <t>T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EAUT_107(70)</t>
+          <t>EAUT_208(126)</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>T4-Ca3, T4-Ca5</t>
+          <t>T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EAUT_203(70)</t>
+          <t>EAUT_306(70)</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1974,59 +1974,59 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EAUT_205(78)</t>
+          <t>EAUT_308(70)</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EAUT_206(78)</t>
+          <t>EAUT_311(70)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EAUT_208(126)</t>
+          <t>EAUT_312(70)</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>T4-Ca4, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EAUT_303(70)</t>
+          <t>EAUT_313(70)</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EAUT_306(70)</t>
+          <t>EAUT_314(70)</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2049,14 +2049,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EAUT_308(70)</t>
+          <t>EAUT_315(70)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2064,119 +2064,119 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>T4-Ca4, T4-Ca5</t>
+          <t>T6-Ca3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EAUT_309(70)</t>
+          <t>EAUT_317(72)</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca5</t>
+          <t>T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EAUT_310(70)</t>
+          <t>EAUT_318(72)</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>T4-Ca2, T4-Ca5</t>
+          <t>T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EAUT_311(70)</t>
+          <t>EAUT_321(72)</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>T4-Ca1, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T4-Ca3, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EAUT_312(70)</t>
+          <t>EAUT_322(80)</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca3, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EAUT_313(70)</t>
+          <t>EAUT_323(72)</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>T4-Ca1, T4-Ca4, T4-Ca5, T6-Ca2</t>
+          <t>T6-Ca3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EAUT_314(70)</t>
+          <t>EAUT_324(72)</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>T4-Ca4, T4-Ca5</t>
+          <t>T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EAUT_315(70)</t>
+          <t>EAUT_326(72)</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EAUT_317(72)</t>
+          <t>EAUT_327(72)</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2184,179 +2184,179 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>T4-Ca5, T6-Ca1</t>
+          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EAUT_318(72)</t>
+          <t>GDTC_100(100)</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca1, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EAUT_321(72)</t>
+          <t>NT_01(100)</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca3, T4-Ca4, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EAUT_322(80)</t>
+          <t>OTO_301(70)</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EAUT_323(72)</t>
+          <t>Online_01(100)</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EAUT_324(72)</t>
+          <t>PLC_1001(120)</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca1, T4-Ca2, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EAUT_325(72)</t>
+          <t>PLC_101 - 2(80)</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EAUT_326(72)</t>
+          <t>PLC_101 - 3(70)</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca1, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EAUT_327(72)</t>
+          <t>PLC_101 - 4(70)</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>T2-Ca1, T4-Ca1, T4-Ca2, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GDTC_100(100)</t>
+          <t>PLC_101 - 5(70)</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NT_01(100)</t>
+          <t>PLC_101 - 6(70)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OTO_301(70)</t>
+          <t>PLC_401(120)</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca3, T4-Ca4, T4-Ca5</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Online_01(100)</t>
+          <t>PLC_604(100)</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2364,44 +2364,44 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PLC_1001(120)</t>
+          <t>PLC_701(100)</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T4-Ca3, T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PLC_101 - 2(80)</t>
+          <t>PLC_801(75)</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PLC_101 - 3(70)</t>
+          <t>TT_102(70)</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2409,44 +2409,44 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLC_101 - 4(70)</t>
+          <t>TT_801(80)</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PLC_101 - 5(70)</t>
+          <t>TT_802(80)</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca4, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PLC_101 - 6(70)</t>
+          <t>VNB_204(70)</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2454,104 +2454,104 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PLC_401(120)</t>
+          <t>VNB_401(70)</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PLC_604(100)</t>
+          <t>VNB_404(92)</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca4, T4-Ca4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PLC_701(100)</t>
+          <t>VNB_406(150)</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>T4-Ca3, T4-Ca4, T4-Ca5</t>
+          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PLC_801(75)</t>
+          <t>VNB_407(150)</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TT_102(70)</t>
+          <t>VNB_408(150)</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TT_701(70)</t>
+          <t>VNB_504(92)</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>T4-Ca1, T4-Ca5</t>
+          <t>T2-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TT_801(80)</t>
+          <t>VNB_506(80)</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2559,202 +2559,37 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca4, T6-Ca4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TT_802(80)</t>
+          <t>VNB_601(800)</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VNB_204(70)</t>
+          <t>Ảo_01(100)</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>VNB_401(70)</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>70</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T4-Ca3, T4-Ca4, T4-Ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>VNB_404(92)</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>92</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>T4-Ca4, T4-Ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>VNB_406(150)</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>150</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>T4-Ca4, T4-Ca5, T6-Ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>VNB_407(150)</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>150</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>T4-Ca2, T4-Ca4, T4-Ca5, T6-Ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>VNB_408(150)</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>150</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T4-Ca2, T4-Ca5, T6-Ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>VNB_504(92)</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>92</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>T4-Ca2, T4-Ca5, T6-Ca1</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>VNB_506(80)</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>80</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>VNB_507(80)</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>80</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>T4-Ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>VNB_508(78)</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>78</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>T4-Ca5</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>VNB_601(800)</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>800</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>T2-Ca1, T2-Ca3, T6-Ca1, T6-Ca2</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Ảo_01(100)</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>100</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>T2-Ca1, T2-Ca3, T4-Ca1, T4-Ca2, T4-Ca3, T4-Ca4, T4-Ca5, T6-Ca1, T6-Ca2</t>
+          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
@@ -1764,44 +1764,44 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DTD_401(76)</t>
+          <t>DTD_603(70)</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>T2-Ca4</t>
+          <t>T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DTD_602(70)</t>
+          <t>DTD_701(126)</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>T6-Ca3, T6-Ca4</t>
+          <t>T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DTD_603(70)</t>
+          <t>DTD_702(70)</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1809,44 +1809,44 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca4, T6-Ca3</t>
+          <t>T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DTD_701(126)</t>
+          <t>DTD_703(70)</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>T2-Ca4, T4-Ca3, T4-Ca4</t>
+          <t>T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DTD_702(70)</t>
+          <t>EAUT_104(72)</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca3, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DTD_703(70)</t>
+          <t>EAUT_105(70)</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1854,29 +1854,29 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EAUT_104(72)</t>
+          <t>EAUT_306(70)</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca3, T6-Ca3</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EAUT_105(70)</t>
+          <t>EAUT_309(70)</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1884,14 +1884,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>T4-Ca4</t>
+          <t>T2-Ca1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EAUT_106(70)</t>
+          <t>EAUT_311(70)</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1899,14 +1899,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>T4-Ca3</t>
+          <t>T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EAUT_107(70)</t>
+          <t>EAUT_312(70)</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1914,404 +1914,404 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>T4-Ca3</t>
+          <t>T2-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EAUT_204(80)</t>
+          <t>EAUT_313(70)</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>T6-Ca4</t>
+          <t>T4-Ca1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EAUT_205(78)</t>
+          <t>EAUT_317(72)</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>T2-Ca4</t>
+          <t>T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EAUT_208(126)</t>
+          <t>EAUT_318(72)</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>T4-Ca4</t>
+          <t>T2-Ca1, T4-Ca1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EAUT_306(70)</t>
+          <t>EAUT_322(80)</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EAUT_308(70)</t>
+          <t>EAUT_323(72)</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EAUT_311(70)</t>
+          <t>EAUT_324(72)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EAUT_312(70)</t>
+          <t>EAUT_325(72)</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EAUT_313(70)</t>
+          <t>EAUT_326(72)</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>T4-Ca4, T6-Ca4</t>
+          <t>T4-Ca1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EAUT_314(70)</t>
+          <t>EAUT_327(72)</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>T4-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EAUT_315(70)</t>
+          <t>GDTC_100(100)</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>T6-Ca3</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EAUT_317(72)</t>
+          <t>NT_01(100)</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EAUT_318(72)</t>
+          <t>OTO_301(70)</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>T2-Ca4</t>
+          <t>T2-Ca1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EAUT_321(72)</t>
+          <t>Online_01(100)</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>T2-Ca3, T4-Ca3, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EAUT_322(80)</t>
+          <t>PLC_1001(120)</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EAUT_323(72)</t>
+          <t>PLC_101 - 2(80)</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>T6-Ca3</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EAUT_324(72)</t>
+          <t>PLC_101 - 3(70)</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>T4-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EAUT_326(72)</t>
+          <t>PLC_101 - 4(70)</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EAUT_327(72)</t>
+          <t>PLC_101 - 5(70)</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GDTC_100(100)</t>
+          <t>PLC_101 - 6(70)</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NT_01(100)</t>
+          <t>PLC_401(120)</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OTO_301(70)</t>
+          <t>PLC_604(100)</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Online_01(100)</t>
+          <t>PLC_801(75)</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PLC_1001(120)</t>
+          <t>TT_102(70)</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PLC_101 - 2(80)</t>
+          <t>TT_701(70)</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T4-Ca1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PLC_101 - 3(70)</t>
+          <t>TT_801(80)</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PLC_101 - 4(70)</t>
+          <t>TT_802(80)</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PLC_101 - 5(70)</t>
+          <t>VNB_204(70)</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2319,59 +2319,59 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PLC_101 - 6(70)</t>
+          <t>VNB_504(92)</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PLC_401(120)</t>
+          <t>VNB_506(80)</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PLC_604(100)</t>
+          <t>VNB_601(800)</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PLC_701(100)</t>
+          <t>Ảo_01(100)</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2379,217 +2379,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>T4-Ca3, T4-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>PLC_801(75)</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>75</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>TT_102(70)</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>70</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>TT_801(80)</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>80</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>TT_802(80)</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>80</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>T2-Ca4, T4-Ca4, T6-Ca3, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>VNB_204(70)</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>70</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>VNB_401(70)</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>70</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>VNB_404(92)</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>92</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>T2-Ca4, T4-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>VNB_406(150)</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>150</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>VNB_407(150)</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>150</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>T2-Ca4, T4-Ca4, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>VNB_408(150)</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>150</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>VNB_504(92)</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>92</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>T2-Ca4, T6-Ca3, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>VNB_506(80)</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>80</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca4, T6-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>VNB_601(800)</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>800</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Ảo_01(100)</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>100</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>T2-Ca3, T2-Ca4, T4-Ca3, T4-Ca4, T6-Ca3, T6-Ca4</t>
+          <t>T2-Ca1, T4-Ca1, T6-Ca1</t>
         </is>
       </c>
     </row>
